--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/KSK_Simf/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/KSK_Simf/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\KSK_Simf\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E760F701-CEDC-400F-AFB3-45BECD95EA61}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEF9EB7-FEEE-418D-A707-A499DB4F0AA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$576</definedName>
-    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$515</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$577</definedName>
+    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$516</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="1024">
   <si>
     <t>1С</t>
   </si>
@@ -3099,6 +3099,18 @@
   </si>
   <si>
     <t>Жареные вареники с картофелем и беконом ТМ Стародворье 0,2 кг  ПОКОМ</t>
+  </si>
+  <si>
+    <t>Наггетсы Сливушки в темпуре ТМ Вязанка флоу-пак 0,23 кг  ПОКОМ</t>
+  </si>
+  <si>
+    <t>SU004023</t>
+  </si>
+  <si>
+    <t>P005157</t>
+  </si>
+  <si>
+    <t>Наггетсы «Сливушки в темпуре» Фикс.вес 0,23 ТМ «Вязанка»</t>
   </si>
 </sst>
 </file>
@@ -6354,7 +6366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H576"/>
+  <dimension ref="A1:H577"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -18237,47 +18249,44 @@
       <c r="G514" s="1"/>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A515" s="17" t="s">
-        <v>783</v>
-      </c>
-      <c r="B515" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="C515" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="D515" s="19">
-        <v>4301071038</v>
-      </c>
-      <c r="E515" s="18">
-        <v>4607111039248</v>
-      </c>
-      <c r="F515" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="G515" s="21"/>
-      <c r="H515" s="22" t="s">
-        <v>844</v>
-      </c>
+      <c r="A515" s="10" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B515" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D515" s="4">
+        <v>4301132243</v>
+      </c>
+      <c r="E515" s="3">
+        <v>4620207491195</v>
+      </c>
+      <c r="F515" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="17" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B516" s="18" t="s">
-        <v>106</v>
+        <v>613</v>
       </c>
       <c r="C516" s="18" t="s">
-        <v>257</v>
+        <v>614</v>
       </c>
       <c r="D516" s="19">
-        <v>4301070981</v>
+        <v>4301071038</v>
       </c>
       <c r="E516" s="18">
-        <v>4607111036728</v>
+        <v>4607111039248</v>
       </c>
       <c r="F516" s="20" t="s">
-        <v>258</v>
+        <v>615</v>
       </c>
       <c r="G516" s="21"/>
       <c r="H516" s="22" t="s">
@@ -18286,22 +18295,22 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="17" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B517" s="18" t="s">
-        <v>621</v>
+        <v>106</v>
       </c>
       <c r="C517" s="18" t="s">
-        <v>622</v>
+        <v>257</v>
       </c>
       <c r="D517" s="19">
-        <v>4301071039</v>
+        <v>4301070981</v>
       </c>
       <c r="E517" s="18">
-        <v>4607111039279</v>
+        <v>4607111036728</v>
       </c>
       <c r="F517" s="20" t="s">
-        <v>623</v>
+        <v>258</v>
       </c>
       <c r="G517" s="21"/>
       <c r="H517" s="22" t="s">
@@ -18310,22 +18319,22 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="17" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B518" s="18" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C518" s="18" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="D518" s="19">
-        <v>4301071051</v>
+        <v>4301071039</v>
       </c>
       <c r="E518" s="18">
-        <v>4607111039262</v>
+        <v>4607111039279</v>
       </c>
       <c r="F518" s="20" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="G518" s="21"/>
       <c r="H518" s="22" t="s">
@@ -18334,22 +18343,22 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B519" s="18" t="s">
-        <v>289</v>
+        <v>609</v>
       </c>
       <c r="C519" s="18" t="s">
-        <v>290</v>
+        <v>610</v>
       </c>
       <c r="D519" s="19">
-        <v>4301132080</v>
+        <v>4301071051</v>
       </c>
       <c r="E519" s="18">
-        <v>4640242180397</v>
+        <v>4607111039262</v>
       </c>
       <c r="F519" s="20" t="s">
-        <v>291</v>
+        <v>611</v>
       </c>
       <c r="G519" s="21"/>
       <c r="H519" s="22" t="s">
@@ -18358,22 +18367,22 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B520" s="18" t="s">
-        <v>111</v>
+        <v>289</v>
       </c>
       <c r="C520" s="18" t="s">
-        <v>517</v>
+        <v>290</v>
       </c>
       <c r="D520" s="19">
-        <v>4301071029</v>
+        <v>4301132080</v>
       </c>
       <c r="E520" s="18">
-        <v>4607111035899</v>
+        <v>4640242180397</v>
       </c>
       <c r="F520" s="20" t="s">
-        <v>112</v>
+        <v>291</v>
       </c>
       <c r="G520" s="21"/>
       <c r="H520" s="22" t="s">
@@ -18382,22 +18391,22 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="17" t="s">
-        <v>789</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D521" s="4">
-        <v>4301136053</v>
-      </c>
-      <c r="E521" s="3">
-        <v>4640242180236</v>
-      </c>
-      <c r="F521" s="5" t="s">
-        <v>300</v>
+        <v>788</v>
+      </c>
+      <c r="B521" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C521" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="D521" s="19">
+        <v>4301071029</v>
+      </c>
+      <c r="E521" s="18">
+        <v>4607111035899</v>
+      </c>
+      <c r="F521" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="G521" s="21"/>
       <c r="H521" s="22" t="s">
@@ -18406,22 +18415,22 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="17" t="s">
-        <v>790</v>
-      </c>
-      <c r="B522" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="C522" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="D522" s="19">
-        <v>4301070977</v>
-      </c>
-      <c r="E522" s="18">
-        <v>4607111037411</v>
-      </c>
-      <c r="F522" s="20" t="s">
-        <v>316</v>
+        <v>789</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D522" s="4">
+        <v>4301136053</v>
+      </c>
+      <c r="E522" s="3">
+        <v>4640242180236</v>
+      </c>
+      <c r="F522" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="G522" s="21"/>
       <c r="H522" s="22" t="s">
@@ -18430,22 +18439,22 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="17" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B523" s="18" t="s">
-        <v>546</v>
+        <v>314</v>
       </c>
       <c r="C523" s="18" t="s">
-        <v>547</v>
+        <v>315</v>
       </c>
       <c r="D523" s="19">
-        <v>4301135375</v>
+        <v>4301070977</v>
       </c>
       <c r="E523" s="18">
-        <v>4640242181486</v>
+        <v>4607111037411</v>
       </c>
       <c r="F523" s="20" t="s">
-        <v>548</v>
+        <v>316</v>
       </c>
       <c r="G523" s="21"/>
       <c r="H523" s="22" t="s">
@@ -18454,70 +18463,70 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="17" t="s">
-        <v>792</v>
-      </c>
-      <c r="B524" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="C524" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="D524" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E524" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F524" s="5" t="s">
-        <v>937</v>
+        <v>791</v>
+      </c>
+      <c r="B524" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="C524" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="D524" s="19">
+        <v>4301135375</v>
+      </c>
+      <c r="E524" s="18">
+        <v>4640242181486</v>
+      </c>
+      <c r="F524" s="20" t="s">
+        <v>548</v>
       </c>
       <c r="G524" s="21"/>
-      <c r="H524" s="16" t="s">
-        <v>931</v>
+      <c r="H524" s="22" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="17" t="s">
-        <v>793</v>
-      </c>
-      <c r="B525" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C525" s="18" t="s">
-        <v>624</v>
-      </c>
-      <c r="D525" s="19">
-        <v>4301071050</v>
-      </c>
-      <c r="E525" s="18">
-        <v>4607111036216</v>
-      </c>
-      <c r="F525" s="20" t="s">
-        <v>625</v>
+        <v>792</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="D525" s="4">
+        <v>4301135760</v>
+      </c>
+      <c r="E525" s="3">
+        <v>4620207491010</v>
+      </c>
+      <c r="F525" s="5" t="s">
+        <v>937</v>
       </c>
       <c r="G525" s="21"/>
-      <c r="H525" s="22" t="s">
-        <v>844</v>
+      <c r="H525" s="16" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="17" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B526" s="18" t="s">
-        <v>617</v>
+        <v>110</v>
       </c>
       <c r="C526" s="18" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D526" s="19">
-        <v>4301071049</v>
+        <v>4301071050</v>
       </c>
       <c r="E526" s="18">
-        <v>4607111039293</v>
+        <v>4607111036216</v>
       </c>
       <c r="F526" s="20" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="G526" s="21"/>
       <c r="H526" s="22" t="s">
@@ -18526,22 +18535,22 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="17" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B527" s="18" t="s">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="C527" s="18" t="s">
-        <v>643</v>
+        <v>618</v>
       </c>
       <c r="D527" s="19">
-        <v>4301135532</v>
+        <v>4301071049</v>
       </c>
       <c r="E527" s="18">
-        <v>4607111033994</v>
+        <v>4607111039293</v>
       </c>
       <c r="F527" s="20" t="s">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="G527" s="21"/>
       <c r="H527" s="22" t="s">
@@ -18550,22 +18559,22 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="17" t="s">
-        <v>796</v>
-      </c>
-      <c r="B528" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="C528" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="D528" s="4">
-        <v>4301135555</v>
-      </c>
-      <c r="E528" s="3">
-        <v>4607111034014</v>
-      </c>
-      <c r="F528" s="5" t="s">
-        <v>647</v>
+        <v>795</v>
+      </c>
+      <c r="B528" s="18" t="s">
+        <v>642</v>
+      </c>
+      <c r="C528" s="18" t="s">
+        <v>643</v>
+      </c>
+      <c r="D528" s="19">
+        <v>4301135532</v>
+      </c>
+      <c r="E528" s="18">
+        <v>4607111033994</v>
+      </c>
+      <c r="F528" s="20" t="s">
+        <v>644</v>
       </c>
       <c r="G528" s="21"/>
       <c r="H528" s="22" t="s">
@@ -18574,70 +18583,70 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>928</v>
+        <v>645</v>
       </c>
       <c r="C529" s="3" t="s">
-        <v>929</v>
+        <v>646</v>
       </c>
       <c r="D529" s="4">
-        <v>4301135793</v>
+        <v>4301135555</v>
       </c>
       <c r="E529" s="3">
-        <v>4620207491003</v>
+        <v>4607111034014</v>
       </c>
       <c r="F529" s="5" t="s">
-        <v>930</v>
+        <v>647</v>
       </c>
       <c r="G529" s="21"/>
-      <c r="H529" s="16" t="s">
-        <v>931</v>
+      <c r="H529" s="22" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="17" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>378</v>
+        <v>928</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>379</v>
+        <v>929</v>
       </c>
       <c r="D530" s="4">
-        <v>4301136052</v>
+        <v>4301135793</v>
       </c>
       <c r="E530" s="3">
-        <v>4640242180410</v>
+        <v>4620207491003</v>
       </c>
       <c r="F530" s="5" t="s">
-        <v>380</v>
+        <v>930</v>
       </c>
       <c r="G530" s="21"/>
-      <c r="H530" s="22" t="s">
-        <v>844</v>
+      <c r="H530" s="16" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="17" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>542</v>
+        <v>378</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>543</v>
+        <v>379</v>
       </c>
       <c r="D531" s="4">
-        <v>4301135518</v>
+        <v>4301136052</v>
       </c>
       <c r="E531" s="3">
-        <v>4640242181561</v>
+        <v>4640242180410</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>544</v>
+        <v>380</v>
       </c>
       <c r="G531" s="21"/>
       <c r="H531" s="22" t="s">
@@ -18646,22 +18655,22 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="17" t="s">
-        <v>800</v>
-      </c>
-      <c r="B532" s="18" t="s">
-        <v>592</v>
-      </c>
-      <c r="C532" s="18" t="s">
-        <v>593</v>
-      </c>
-      <c r="D532" s="19">
-        <v>4301135374</v>
-      </c>
-      <c r="E532" s="18">
-        <v>4640242181424</v>
-      </c>
-      <c r="F532" s="20" t="s">
-        <v>594</v>
+        <v>799</v>
+      </c>
+      <c r="B532" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D532" s="4">
+        <v>4301135518</v>
+      </c>
+      <c r="E532" s="3">
+        <v>4640242181561</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>544</v>
       </c>
       <c r="G532" s="21"/>
       <c r="H532" s="22" t="s">
@@ -18670,22 +18679,22 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B533" s="18" t="s">
-        <v>845</v>
+        <v>592</v>
       </c>
       <c r="C533" s="18" t="s">
-        <v>846</v>
+        <v>593</v>
       </c>
       <c r="D533" s="19">
-        <v>4301132079</v>
+        <v>4301135374</v>
       </c>
       <c r="E533" s="18">
-        <v>4607111038487</v>
+        <v>4640242181424</v>
       </c>
       <c r="F533" s="20" t="s">
-        <v>421</v>
+        <v>594</v>
       </c>
       <c r="G533" s="21"/>
       <c r="H533" s="22" t="s">
@@ -18694,22 +18703,22 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="17" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B534" s="18" t="s">
-        <v>160</v>
+        <v>845</v>
       </c>
       <c r="C534" s="18" t="s">
-        <v>627</v>
+        <v>846</v>
       </c>
       <c r="D534" s="19">
-        <v>4301071056</v>
+        <v>4301132079</v>
       </c>
       <c r="E534" s="18">
-        <v>4640242180250</v>
+        <v>4607111038487</v>
       </c>
       <c r="F534" s="20" t="s">
-        <v>628</v>
+        <v>421</v>
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="22" t="s">
@@ -18718,22 +18727,22 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="17" t="s">
-        <v>803</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C535" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D535" s="4">
-        <v>4301136051</v>
-      </c>
-      <c r="E535" s="3">
-        <v>4640242180304</v>
-      </c>
-      <c r="F535" s="5" t="s">
-        <v>297</v>
+        <v>802</v>
+      </c>
+      <c r="B535" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C535" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="D535" s="19">
+        <v>4301071056</v>
+      </c>
+      <c r="E535" s="18">
+        <v>4640242180250</v>
+      </c>
+      <c r="F535" s="20" t="s">
+        <v>628</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="22" t="s">
@@ -18742,22 +18751,22 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>995</v>
+        <v>295</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>996</v>
+        <v>296</v>
       </c>
       <c r="D536" s="4">
-        <v>4301071109</v>
+        <v>4301136051</v>
       </c>
       <c r="E536" s="3">
-        <v>4607111035929</v>
+        <v>4640242180304</v>
       </c>
       <c r="F536" s="5" t="s">
-        <v>997</v>
+        <v>297</v>
       </c>
       <c r="G536" s="21"/>
       <c r="H536" s="22" t="s">
@@ -18766,22 +18775,22 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>733</v>
+        <v>995</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>734</v>
+        <v>996</v>
       </c>
       <c r="D537" s="4">
-        <v>4301135550</v>
+        <v>4301071109</v>
       </c>
       <c r="E537" s="3">
-        <v>4607111034199</v>
+        <v>4607111035929</v>
       </c>
       <c r="F537" s="5" t="s">
-        <v>735</v>
+        <v>997</v>
       </c>
       <c r="G537" s="21"/>
       <c r="H537" s="22" t="s">
@@ -18790,22 +18799,22 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="17" t="s">
-        <v>806</v>
-      </c>
-      <c r="B538" s="18" t="s">
-        <v>730</v>
-      </c>
-      <c r="C538" s="18" t="s">
-        <v>731</v>
-      </c>
-      <c r="D538" s="19">
-        <v>4301132186</v>
-      </c>
-      <c r="E538" s="18">
-        <v>4607111036520</v>
-      </c>
-      <c r="F538" s="20" t="s">
-        <v>732</v>
+        <v>805</v>
+      </c>
+      <c r="B538" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="D538" s="4">
+        <v>4301135550</v>
+      </c>
+      <c r="E538" s="3">
+        <v>4607111034199</v>
+      </c>
+      <c r="F538" s="5" t="s">
+        <v>735</v>
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
@@ -18814,22 +18823,22 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B539" s="18" t="s">
-        <v>605</v>
+        <v>730</v>
       </c>
       <c r="C539" s="18" t="s">
-        <v>606</v>
+        <v>731</v>
       </c>
       <c r="D539" s="19">
-        <v>4301071047</v>
+        <v>4301132186</v>
       </c>
       <c r="E539" s="18">
-        <v>4607111039330</v>
+        <v>4607111036520</v>
       </c>
       <c r="F539" s="20" t="s">
-        <v>607</v>
+        <v>732</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="22" t="s">
@@ -18838,22 +18847,22 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="17" t="s">
-        <v>808</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C540" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="D540" s="4">
-        <v>4301131047</v>
-      </c>
-      <c r="E540" s="3">
-        <v>4607111034120</v>
-      </c>
-      <c r="F540" s="5" t="s">
-        <v>774</v>
+        <v>807</v>
+      </c>
+      <c r="B540" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="C540" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="D540" s="19">
+        <v>4301071047</v>
+      </c>
+      <c r="E540" s="18">
+        <v>4607111039330</v>
+      </c>
+      <c r="F540" s="20" t="s">
+        <v>607</v>
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="22" t="s">
@@ -18862,70 +18871,70 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>891</v>
+        <v>772</v>
       </c>
       <c r="C541" s="3" t="s">
-        <v>892</v>
+        <v>773</v>
       </c>
       <c r="D541" s="4">
-        <v>4301135763</v>
+        <v>4301131047</v>
       </c>
       <c r="E541" s="3">
-        <v>4620207491027</v>
+        <v>4607111034120</v>
       </c>
       <c r="F541" s="5" t="s">
-        <v>893</v>
+        <v>774</v>
       </c>
       <c r="G541" s="21"/>
       <c r="H541" s="22" t="s">
-        <v>950</v>
+        <v>844</v>
       </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="17" t="s">
-        <v>810</v>
-      </c>
-      <c r="B542" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="C542" s="18" t="s">
-        <v>551</v>
-      </c>
-      <c r="D542" s="19">
-        <v>4301135405</v>
-      </c>
-      <c r="E542" s="18">
-        <v>4640242181523</v>
-      </c>
-      <c r="F542" s="20" t="s">
-        <v>552</v>
+        <v>809</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="D542" s="4">
+        <v>4301135763</v>
+      </c>
+      <c r="E542" s="3">
+        <v>4620207491027</v>
+      </c>
+      <c r="F542" s="5" t="s">
+        <v>893</v>
       </c>
       <c r="G542" s="21"/>
       <c r="H542" s="22" t="s">
-        <v>844</v>
+        <v>950</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B543" s="18" t="s">
-        <v>697</v>
+        <v>550</v>
       </c>
       <c r="C543" s="18" t="s">
-        <v>698</v>
+        <v>551</v>
       </c>
       <c r="D543" s="19">
-        <v>4301135402</v>
+        <v>4301135405</v>
       </c>
       <c r="E543" s="18">
-        <v>4640242181493</v>
+        <v>4640242181523</v>
       </c>
       <c r="F543" s="20" t="s">
-        <v>696</v>
+        <v>552</v>
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
@@ -18934,22 +18943,22 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="17" t="s">
-        <v>812</v>
-      </c>
-      <c r="B544" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="C544" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="D544" s="4">
-        <v>4301131046</v>
-      </c>
-      <c r="E544" s="3">
-        <v>4607111034137</v>
-      </c>
-      <c r="F544" s="5" t="s">
-        <v>872</v>
+        <v>811</v>
+      </c>
+      <c r="B544" s="18" t="s">
+        <v>697</v>
+      </c>
+      <c r="C544" s="18" t="s">
+        <v>698</v>
+      </c>
+      <c r="D544" s="19">
+        <v>4301135402</v>
+      </c>
+      <c r="E544" s="18">
+        <v>4640242181493</v>
+      </c>
+      <c r="F544" s="20" t="s">
+        <v>696</v>
       </c>
       <c r="G544" s="21"/>
       <c r="H544" s="22" t="s">
@@ -18958,22 +18967,22 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C545" s="3" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="D545" s="4">
-        <v>4301136079</v>
+        <v>4301131046</v>
       </c>
       <c r="E545" s="3">
-        <v>4607025784319</v>
+        <v>4607111034137</v>
       </c>
       <c r="F545" s="5" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="G545" s="21"/>
       <c r="H545" s="22" t="s">
@@ -18982,22 +18991,22 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="17" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>944</v>
+        <v>876</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>945</v>
+        <v>877</v>
       </c>
       <c r="D546" s="4">
-        <v>4301135753</v>
+        <v>4301136079</v>
       </c>
       <c r="E546" s="3">
-        <v>4620207490914</v>
+        <v>4607025784319</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>946</v>
+        <v>878</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
@@ -19006,70 +19015,70 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="D547" s="4">
-        <v>4301135778</v>
+        <v>4301135753</v>
       </c>
       <c r="E547" s="3">
-        <v>4620207490853</v>
+        <v>4620207490914</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="G547" s="21"/>
-      <c r="H547" s="16" t="s">
-        <v>938</v>
+      <c r="H547" s="22" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="17" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>860</v>
+        <v>932</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>861</v>
+        <v>933</v>
       </c>
       <c r="D548" s="4">
-        <v>4301132179</v>
+        <v>4301135778</v>
       </c>
       <c r="E548" s="3">
-        <v>4607111035691</v>
+        <v>4620207490853</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>862</v>
+        <v>934</v>
       </c>
       <c r="G548" s="21"/>
-      <c r="H548" s="22" t="s">
-        <v>844</v>
+      <c r="H548" s="16" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="17" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>727</v>
+        <v>860</v>
       </c>
       <c r="C549" s="3" t="s">
-        <v>728</v>
+        <v>861</v>
       </c>
       <c r="D549" s="4">
-        <v>4301132190</v>
+        <v>4301132179</v>
       </c>
       <c r="E549" s="3">
-        <v>4607111036537</v>
+        <v>4607111035691</v>
       </c>
       <c r="F549" s="5" t="s">
-        <v>729</v>
+        <v>862</v>
       </c>
       <c r="G549" s="21"/>
       <c r="H549" s="22" t="s">
@@ -19078,22 +19087,22 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="17" t="s">
-        <v>818</v>
-      </c>
-      <c r="B550" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C550" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D550" s="19">
-        <v>4301131019</v>
-      </c>
-      <c r="E550" s="18">
-        <v>4640242180427</v>
-      </c>
-      <c r="F550" s="20" t="s">
-        <v>373</v>
+        <v>817</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D550" s="4">
+        <v>4301132190</v>
+      </c>
+      <c r="E550" s="3">
+        <v>4607111036537</v>
+      </c>
+      <c r="F550" s="5" t="s">
+        <v>729</v>
       </c>
       <c r="G550" s="21"/>
       <c r="H550" s="22" t="s">
@@ -19102,22 +19111,22 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="17" t="s">
-        <v>819</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="C551" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="D551" s="4">
-        <v>4301135571</v>
-      </c>
-      <c r="E551" s="3">
-        <v>4607111035028</v>
-      </c>
-      <c r="F551" s="5" t="s">
-        <v>881</v>
+        <v>818</v>
+      </c>
+      <c r="B551" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C551" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D551" s="19">
+        <v>4301131019</v>
+      </c>
+      <c r="E551" s="18">
+        <v>4640242180427</v>
+      </c>
+      <c r="F551" s="20" t="s">
+        <v>373</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
@@ -19126,70 +19135,70 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="D552" s="4">
+        <v>4301135571</v>
+      </c>
+      <c r="E552" s="3">
+        <v>4607111035028</v>
+      </c>
+      <c r="F552" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="G552" s="21"/>
+      <c r="H552" s="22" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A553" s="17" t="s">
         <v>820</v>
       </c>
-      <c r="B552" s="3" t="s">
+      <c r="B553" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="C552" s="3" t="s">
+      <c r="C553" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="D552" s="4">
+      <c r="D553" s="4">
         <v>4301135768</v>
       </c>
-      <c r="E552" s="3">
+      <c r="E553" s="3">
         <v>4620207491034</v>
       </c>
-      <c r="F552" s="5" t="s">
+      <c r="F553" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="G552" s="21"/>
-      <c r="H552" s="16" t="s">
+      <c r="G553" s="21"/>
+      <c r="H553" s="16" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="553" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A553" s="17" t="s">
+    <row r="554" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A554" s="17" t="s">
         <v>822</v>
       </c>
-      <c r="B553" s="18" t="s">
+      <c r="B554" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="C553" s="18" t="s">
+      <c r="C554" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="D553" s="19">
+      <c r="D554" s="19">
         <v>4301070960</v>
       </c>
-      <c r="E553" s="18">
+      <c r="E554" s="18">
         <v>4607111038623</v>
       </c>
-      <c r="F553" s="20" t="s">
+      <c r="F554" s="20" t="s">
         <v>485</v>
-      </c>
-      <c r="G553" s="21"/>
-      <c r="H553" s="22" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A554" s="17" t="s">
-        <v>823</v>
-      </c>
-      <c r="B554" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C554" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="D554" s="19">
-        <v>4301070966</v>
-      </c>
-      <c r="E554" s="18">
-        <v>4607111038135</v>
-      </c>
-      <c r="F554" s="20" t="s">
-        <v>363</v>
       </c>
       <c r="G554" s="21"/>
       <c r="H554" s="22" t="s">
@@ -19197,71 +19206,71 @@
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A555" s="10" t="s">
+      <c r="A555" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="B555" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C555" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="D555" s="19">
+        <v>4301070966</v>
+      </c>
+      <c r="E555" s="18">
+        <v>4607111038135</v>
+      </c>
+      <c r="F555" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="G555" s="21"/>
+      <c r="H555" s="22" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A556" s="10" t="s">
         <v>888</v>
       </c>
-      <c r="B555" s="3" t="s">
+      <c r="B556" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="C555" s="3" t="s">
+      <c r="C556" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="D555" s="4">
+      <c r="D556" s="4">
         <v>4301070990</v>
       </c>
-      <c r="E555" s="3">
+      <c r="E556" s="3">
         <v>4607111038494</v>
       </c>
-      <c r="F555" s="5" t="s">
+      <c r="F556" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="G555" s="1"/>
-      <c r="H555" s="16" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A556" s="17" t="s">
-        <v>824</v>
-      </c>
-      <c r="B556" s="18" t="s">
-        <v>847</v>
-      </c>
-      <c r="C556" s="18" t="s">
-        <v>848</v>
-      </c>
-      <c r="D556" s="19">
-        <v>4301070990</v>
-      </c>
-      <c r="E556" s="18">
-        <v>4607111038494</v>
-      </c>
-      <c r="F556" s="20" t="s">
-        <v>849</v>
-      </c>
-      <c r="G556" s="21"/>
-      <c r="H556" s="22" t="s">
+      <c r="G556" s="1"/>
+      <c r="H556" s="16" t="s">
         <v>844</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="17" t="s">
-        <v>825</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C557" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D557" s="4">
-        <v>4301071105</v>
-      </c>
-      <c r="E557" s="3">
-        <v>4607111035110</v>
-      </c>
-      <c r="F557" s="5" t="s">
-        <v>1011</v>
+        <v>824</v>
+      </c>
+      <c r="B557" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="C557" s="18" t="s">
+        <v>848</v>
+      </c>
+      <c r="D557" s="19">
+        <v>4301070990</v>
+      </c>
+      <c r="E557" s="18">
+        <v>4607111038494</v>
+      </c>
+      <c r="F557" s="20" t="s">
+        <v>849</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19270,22 +19279,22 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D558" s="4">
-        <v>4301135824</v>
+        <v>4301071105</v>
       </c>
       <c r="E558" s="3">
-        <v>4607111039095</v>
+        <v>4607111035110</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="22" t="s">
@@ -19294,22 +19303,22 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="17" t="s">
-        <v>827</v>
-      </c>
-      <c r="B559" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C559" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="D559" s="19">
-        <v>4301135285</v>
-      </c>
-      <c r="E559" s="18">
-        <v>4607111036407</v>
-      </c>
-      <c r="F559" s="20" t="s">
-        <v>182</v>
+        <v>826</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D559" s="4">
+        <v>4301135824</v>
+      </c>
+      <c r="E559" s="3">
+        <v>4607111039095</v>
+      </c>
+      <c r="F559" s="5" t="s">
+        <v>1005</v>
       </c>
       <c r="G559" s="21"/>
       <c r="H559" s="22" t="s">
@@ -19318,22 +19327,22 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="B560" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="C560" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="D560" s="4">
-        <v>4301135607</v>
-      </c>
-      <c r="E560" s="3">
-        <v>4607111039613</v>
-      </c>
-      <c r="F560" s="5" t="s">
-        <v>703</v>
+        <v>827</v>
+      </c>
+      <c r="B560" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C560" s="18" t="s">
+        <v>519</v>
+      </c>
+      <c r="D560" s="19">
+        <v>4301135285</v>
+      </c>
+      <c r="E560" s="18">
+        <v>4607111036407</v>
+      </c>
+      <c r="F560" s="20" t="s">
+        <v>182</v>
       </c>
       <c r="G560" s="21"/>
       <c r="H560" s="22" t="s">
@@ -19342,22 +19351,22 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="B561" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C561" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D561" s="19">
-        <v>4301080153</v>
-      </c>
-      <c r="E561" s="18">
-        <v>4607111036827</v>
-      </c>
-      <c r="F561" s="20" t="s">
-        <v>127</v>
+        <v>703</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D561" s="4">
+        <v>4301135607</v>
+      </c>
+      <c r="E561" s="3">
+        <v>4607111039613</v>
+      </c>
+      <c r="F561" s="5" t="s">
+        <v>703</v>
       </c>
       <c r="G561" s="21"/>
       <c r="H561" s="22" t="s">
@@ -19366,22 +19375,22 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="17" t="s">
-        <v>829</v>
-      </c>
-      <c r="B562" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="C562" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="D562" s="4">
-        <v>4301135574</v>
-      </c>
-      <c r="E562" s="3">
-        <v>4607111033659</v>
-      </c>
-      <c r="F562" s="5" t="s">
-        <v>717</v>
+        <v>828</v>
+      </c>
+      <c r="B562" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C562" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D562" s="19">
+        <v>4301080153</v>
+      </c>
+      <c r="E562" s="18">
+        <v>4607111036827</v>
+      </c>
+      <c r="F562" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="G562" s="21"/>
       <c r="H562" s="22" t="s">
@@ -19390,22 +19399,22 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="17" t="s">
-        <v>830</v>
-      </c>
-      <c r="B563" s="18" t="s">
-        <v>659</v>
-      </c>
-      <c r="C563" s="18" t="s">
-        <v>660</v>
-      </c>
-      <c r="D563" s="19">
-        <v>4301071044</v>
-      </c>
-      <c r="E563" s="18">
-        <v>4607111039385</v>
-      </c>
-      <c r="F563" s="20" t="s">
-        <v>661</v>
+        <v>829</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D563" s="4">
+        <v>4301135574</v>
+      </c>
+      <c r="E563" s="3">
+        <v>4607111033659</v>
+      </c>
+      <c r="F563" s="5" t="s">
+        <v>717</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="22" t="s">
@@ -19414,22 +19423,22 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B564" s="18" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="C564" s="18" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="D564" s="19">
-        <v>4301071031</v>
+        <v>4301071044</v>
       </c>
       <c r="E564" s="18">
-        <v>4607111038982</v>
+        <v>4607111039385</v>
       </c>
       <c r="F564" s="20" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="G564" s="21"/>
       <c r="H564" s="22" t="s">
@@ -19438,22 +19447,22 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="17" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B565" s="18" t="s">
-        <v>177</v>
+        <v>676</v>
       </c>
       <c r="C565" s="18" t="s">
-        <v>178</v>
+        <v>677</v>
       </c>
       <c r="D565" s="19">
-        <v>4301070917</v>
+        <v>4301071031</v>
       </c>
       <c r="E565" s="18">
-        <v>4607111035912</v>
+        <v>4607111038982</v>
       </c>
       <c r="F565" s="20" t="s">
-        <v>179</v>
+        <v>678</v>
       </c>
       <c r="G565" s="21"/>
       <c r="H565" s="22" t="s">
@@ -19462,22 +19471,22 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="B566" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C566" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="D566" s="4">
-        <v>4301136070</v>
-      </c>
-      <c r="E566" s="3">
-        <v>4607025784012</v>
-      </c>
-      <c r="F566" s="5" t="s">
-        <v>166</v>
+        <v>832</v>
+      </c>
+      <c r="B566" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C566" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="D566" s="19">
+        <v>4301070917</v>
+      </c>
+      <c r="E566" s="18">
+        <v>4607111035912</v>
+      </c>
+      <c r="F566" s="20" t="s">
+        <v>179</v>
       </c>
       <c r="G566" s="21"/>
       <c r="H566" s="22" t="s">
@@ -19486,46 +19495,46 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="17" t="s">
-        <v>834</v>
-      </c>
-      <c r="B567" s="18" t="s">
-        <v>601</v>
-      </c>
-      <c r="C567" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="D567" s="19">
-        <v>4301071046</v>
-      </c>
-      <c r="E567" s="18">
-        <v>4607111039354</v>
-      </c>
-      <c r="F567" s="20" t="s">
-        <v>603</v>
+        <v>833</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D567" s="4">
+        <v>4301136070</v>
+      </c>
+      <c r="E567" s="3">
+        <v>4607025784012</v>
+      </c>
+      <c r="F567" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="568" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="17" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B568" s="18" t="s">
-        <v>850</v>
+        <v>601</v>
       </c>
       <c r="C568" s="18" t="s">
-        <v>851</v>
+        <v>602</v>
       </c>
       <c r="D568" s="19">
-        <v>4301070959</v>
+        <v>4301071046</v>
       </c>
       <c r="E568" s="18">
-        <v>4607111038616</v>
+        <v>4607111039354</v>
       </c>
       <c r="F568" s="20" t="s">
-        <v>852</v>
+        <v>603</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19534,46 +19543,46 @@
     </row>
     <row r="569" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A569" s="17" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B569" s="18" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C569" s="18" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D569" s="19">
-        <v>4301070962</v>
+        <v>4301070959</v>
       </c>
       <c r="E569" s="18">
-        <v>4607111038609</v>
+        <v>4607111038616</v>
       </c>
       <c r="F569" s="20" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A570" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B570" s="18" t="s">
-        <v>250</v>
+        <v>853</v>
       </c>
       <c r="C570" s="18" t="s">
-        <v>251</v>
+        <v>854</v>
       </c>
       <c r="D570" s="19">
-        <v>4301070948</v>
+        <v>4301070962</v>
       </c>
       <c r="E570" s="18">
-        <v>4607111037022</v>
+        <v>4607111038609</v>
       </c>
       <c r="F570" s="20" t="s">
-        <v>150</v>
+        <v>855</v>
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
@@ -19582,22 +19591,22 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="17" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B571" s="18" t="s">
-        <v>690</v>
+        <v>250</v>
       </c>
       <c r="C571" s="18" t="s">
-        <v>691</v>
+        <v>251</v>
       </c>
       <c r="D571" s="19">
-        <v>4301135570</v>
+        <v>4301070948</v>
       </c>
       <c r="E571" s="18">
-        <v>4607111035806</v>
+        <v>4607111037022</v>
       </c>
       <c r="F571" s="20" t="s">
-        <v>692</v>
+        <v>150</v>
       </c>
       <c r="G571" s="21"/>
       <c r="H571" s="22" t="s">
@@ -19606,22 +19615,22 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="17" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B572" s="18" t="s">
-        <v>719</v>
+        <v>690</v>
       </c>
       <c r="C572" s="18" t="s">
-        <v>720</v>
+        <v>691</v>
       </c>
       <c r="D572" s="19">
-        <v>4301071032</v>
+        <v>4301135570</v>
       </c>
       <c r="E572" s="18">
-        <v>4607111038999</v>
+        <v>4607111035806</v>
       </c>
       <c r="F572" s="20" t="s">
-        <v>721</v>
+        <v>692</v>
       </c>
       <c r="G572" s="21"/>
       <c r="H572" s="22" t="s">
@@ -19630,22 +19639,22 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B573" s="18" t="s">
-        <v>663</v>
+        <v>719</v>
       </c>
       <c r="C573" s="18" t="s">
-        <v>664</v>
+        <v>720</v>
       </c>
       <c r="D573" s="19">
-        <v>4301071045</v>
+        <v>4301071032</v>
       </c>
       <c r="E573" s="18">
-        <v>4607111039392</v>
+        <v>4607111038999</v>
       </c>
       <c r="F573" s="20" t="s">
-        <v>665</v>
+        <v>721</v>
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
@@ -19654,22 +19663,22 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="17" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B574" s="18" t="s">
-        <v>479</v>
+        <v>663</v>
       </c>
       <c r="C574" s="18" t="s">
-        <v>480</v>
+        <v>664</v>
       </c>
       <c r="D574" s="19">
-        <v>4301070963</v>
+        <v>4301071045</v>
       </c>
       <c r="E574" s="18">
-        <v>4607111038630</v>
+        <v>4607111039392</v>
       </c>
       <c r="F574" s="20" t="s">
-        <v>481</v>
+        <v>665</v>
       </c>
       <c r="G574" s="21"/>
       <c r="H574" s="22" t="s">
@@ -19678,22 +19687,22 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B575" s="18" t="s">
-        <v>583</v>
+        <v>479</v>
       </c>
       <c r="C575" s="18" t="s">
-        <v>584</v>
+        <v>480</v>
       </c>
       <c r="D575" s="19">
-        <v>4301071054</v>
+        <v>4301070963</v>
       </c>
       <c r="E575" s="18">
-        <v>4607111035639</v>
+        <v>4607111038630</v>
       </c>
       <c r="F575" s="20" t="s">
-        <v>585</v>
+        <v>481</v>
       </c>
       <c r="G575" s="21"/>
       <c r="H575" s="22" t="s">
@@ -19702,30 +19711,54 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B576" s="18" t="s">
-        <v>336</v>
+        <v>583</v>
       </c>
       <c r="C576" s="18" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="D576" s="19">
-        <v>4301135540</v>
+        <v>4301071054</v>
       </c>
       <c r="E576" s="18">
-        <v>4607111035646</v>
+        <v>4607111035639</v>
       </c>
       <c r="F576" s="20" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="G576" s="21"/>
       <c r="H576" s="22" t="s">
         <v>844</v>
       </c>
     </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A577" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="B577" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C577" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="D577" s="19">
+        <v>4301135540</v>
+      </c>
+      <c r="E577" s="18">
+        <v>4607111035646</v>
+      </c>
+      <c r="F577" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="G577" s="21"/>
+      <c r="H577" s="22" t="s">
+        <v>844</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F576" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F577" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F255">
       <sortCondition ref="A1:A185"/>
     </sortState>
